--- a/PIC_2026_Tracker.xlsx
+++ b/PIC_2026_Tracker.xlsx
@@ -2345,7 +2345,7 @@
       </c>
       <c r="J20" s="140" t="inlineStr">
         <is>
-          <t>Partial — $10 SGM still pending</t>
+          <t>$20 cash bet lost; $10 SGM on row 21 (settled loss)</t>
         </is>
       </c>
     </row>
@@ -2374,23 +2374,21 @@
       <c r="F21" s="151" t="n">
         <v>10</v>
       </c>
-      <c r="G21" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G21" s="149" t="n">
+        <v>0</v>
       </c>
       <c r="H21" s="149" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Loss</t>
         </is>
       </c>
       <c r="I21" s="153">
-        <f>IF(G20="",I19+C20,I19+C20+G20)</f>
-        <v/>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Pot. $117.50 | U178.5 pts, GEE H2H, Weitering/Dangerfield/De Koning 10+ disp, McGovern/Mannagh/S.Neale/Kemp 1+ goal</t>
+        <f>IF(G21="",I20+C21,I20+C21+G21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="88" t="inlineStr">
+        <is>
+          <t>SGM lost — Carlton v Geelong Cats 29 May</t>
         </is>
       </c>
     </row>
@@ -2408,17 +2406,27 @@
       <c r="C22" s="143" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="135" t="n"/>
+      <c r="D22" s="135" t="inlineStr">
+        <is>
+          <t>Eagle Farm Race 6 — Brave Monarch</t>
+        </is>
+      </c>
       <c r="E22" s="136" t="n">
-        <v>30</v>
+        <v>3.9</v>
       </c>
       <c r="F22" s="143" t="n">
         <v>30</v>
       </c>
-      <c r="G22" s="137" t="n"/>
-      <c r="H22" s="154" t="n"/>
+      <c r="G22" s="137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="154" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="I22" s="144">
-        <f>IF(G21="",I20+C21,I20+C21+G21)</f>
+        <f>IF(G22="",I21+C22,I21+C22+G22)</f>
         <v/>
       </c>
       <c r="J22" s="140" t="n"/>
@@ -2437,17 +2445,25 @@
       <c r="C23" s="145" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="135" t="n"/>
-      <c r="E23" s="136" t="n">
-        <v>30</v>
-      </c>
+      <c r="D23" s="135" t="inlineStr">
+        <is>
+          <t>Sports Multi — Crusaders, Broncos, Panthers, Bulldogs, QLD State of Origin</t>
+        </is>
+      </c>
+      <c r="E23" s="136" t="n"/>
       <c r="F23" s="145" t="n">
         <v>30</v>
       </c>
-      <c r="G23" s="137" t="n"/>
-      <c r="H23" s="154" t="n"/>
+      <c r="G23" s="137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="154" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="I23" s="146">
-        <f>IF(G22="",I21+C22,I21+C22+G22)</f>
+        <f>IF(G23="",I22+C23,I22+C23+G23)</f>
         <v/>
       </c>
       <c r="J23" s="140" t="n"/>
@@ -2466,17 +2482,25 @@
       <c r="C24" s="134" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="135" t="n"/>
-      <c r="E24" s="136" t="n">
-        <v>30</v>
-      </c>
+      <c r="D24" s="135" t="inlineStr">
+        <is>
+          <t>Various Horses</t>
+        </is>
+      </c>
+      <c r="E24" s="136" t="n"/>
       <c r="F24" s="134" t="n">
         <v>30</v>
       </c>
-      <c r="G24" s="137" t="n"/>
-      <c r="H24" s="154" t="n"/>
+      <c r="G24" s="137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="154" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="I24" s="139">
-        <f>IF(G23="",I22+C23,I22+C23+G23)</f>
+        <f>IF(G24="",I23+C24,I23+C24+G24)</f>
         <v/>
       </c>
       <c r="J24" s="140" t="n"/>
@@ -2495,17 +2519,27 @@
       <c r="C25" s="141" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="135" t="n"/>
+      <c r="D25" s="135" t="inlineStr">
+        <is>
+          <t>Flemington Race 3 — Vegas Jack (Place)</t>
+        </is>
+      </c>
       <c r="E25" s="136" t="n">
-        <v>30</v>
+        <v>2.88</v>
       </c>
       <c r="F25" s="141" t="n">
         <v>30</v>
       </c>
-      <c r="G25" s="137" t="n"/>
-      <c r="H25" s="154" t="n"/>
+      <c r="G25" s="137" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="H25" s="154" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="I25" s="142">
-        <f>IF(G24="",I23+C24,I23+C24+G24)</f>
+        <f>IF(G25="",I24+C25,I24+C25+G25)</f>
         <v/>
       </c>
       <c r="J25" s="140" t="n"/>
@@ -2534,10 +2568,14 @@
       <c r="G26" s="137" t="n"/>
       <c r="H26" s="154" t="n"/>
       <c r="I26" s="144">
-        <f>IF(G25="",I24+C25,I24+C25+G25)</f>
-        <v/>
-      </c>
-      <c r="J26" s="140" t="n"/>
+        <f>IF(G26="",I25+C26,I25+C26+G26)</f>
+        <v/>
+      </c>
+      <c r="J26" s="140" t="inlineStr">
+        <is>
+          <t>BET OUTSTANDING</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="19.5" customHeight="1" s="89">
       <c r="A27" s="120" t="inlineStr">
@@ -2563,7 +2601,7 @@
       <c r="G27" s="137" t="n"/>
       <c r="H27" s="154" t="n"/>
       <c r="I27" s="146">
-        <f>IF(G26="",I25+C26,I25+C26+G26)</f>
+        <f>IF(G27="",I26+C27,I26+C27+G27)</f>
         <v/>
       </c>
       <c r="J27" s="140" t="n"/>
@@ -2592,7 +2630,7 @@
       <c r="G28" s="137" t="n"/>
       <c r="H28" s="154" t="n"/>
       <c r="I28" s="139">
-        <f>IF(G27="",I26+C27,I26+C27+G27)</f>
+        <f>IF(G28="",I27+C28,I27+C28+G28)</f>
         <v/>
       </c>
       <c r="J28" s="140" t="n"/>
@@ -2621,7 +2659,7 @@
       <c r="G29" s="137" t="n"/>
       <c r="H29" s="154" t="n"/>
       <c r="I29" s="142">
-        <f>IF(G28="",I27+C28,I27+C28+G28)</f>
+        <f>IF(G29="",I28+C29,I28+C29+G29)</f>
         <v/>
       </c>
       <c r="J29" s="140" t="n"/>
@@ -2650,7 +2688,7 @@
       <c r="G30" s="137" t="n"/>
       <c r="H30" s="154" t="n"/>
       <c r="I30" s="144">
-        <f>IF(G29="",I28+C29,I28+C29+G29)</f>
+        <f>IF(G30="",I29+C30,I29+C30+G30)</f>
         <v/>
       </c>
       <c r="J30" s="140" t="n"/>
@@ -2679,7 +2717,7 @@
       <c r="G31" s="137" t="n"/>
       <c r="H31" s="154" t="n"/>
       <c r="I31" s="146">
-        <f>IF(G30="",I29+C30,I29+C30+G30)</f>
+        <f>IF(G31="",I30+C31,I30+C31+G31)</f>
         <v/>
       </c>
       <c r="J31" s="140" t="n"/>
@@ -2708,7 +2746,7 @@
       <c r="G32" s="137" t="n"/>
       <c r="H32" s="154" t="n"/>
       <c r="I32" s="139">
-        <f>IF(G31="",I30+C31,I30+C31+G31)</f>
+        <f>IF(G32="",I31+C32,I31+C32+G32)</f>
         <v/>
       </c>
       <c r="J32" s="140" t="n"/>
@@ -2737,7 +2775,7 @@
       <c r="G33" s="137" t="n"/>
       <c r="H33" s="154" t="n"/>
       <c r="I33" s="142">
-        <f>IF(G32="",I31+C32,I31+C32+G32)</f>
+        <f>IF(G33="",I32+C33,I32+C33+G33)</f>
         <v/>
       </c>
       <c r="J33" s="140" t="n"/>
@@ -2766,7 +2804,7 @@
       <c r="G34" s="137" t="n"/>
       <c r="H34" s="154" t="n"/>
       <c r="I34" s="144">
-        <f>IF(G33="",I32+C33,I32+C33+G33)</f>
+        <f>IF(G34="",I33+C34,I33+C34+G34)</f>
         <v/>
       </c>
       <c r="J34" s="140" t="n"/>
@@ -2795,7 +2833,7 @@
       <c r="G35" s="137" t="n"/>
       <c r="H35" s="154" t="n"/>
       <c r="I35" s="146">
-        <f>IF(G34="",I33+C34,I33+C34+G34)</f>
+        <f>IF(G35="",I34+C35,I34+C35+G35)</f>
         <v/>
       </c>
       <c r="J35" s="140" t="n"/>
@@ -2824,7 +2862,7 @@
       <c r="G36" s="137" t="n"/>
       <c r="H36" s="154" t="n"/>
       <c r="I36" s="139">
-        <f>IF(G35="",I34+C35,I34+C35+G35)</f>
+        <f>IF(G36="",I35+C36,I35+C36+G36)</f>
         <v/>
       </c>
       <c r="J36" s="140" t="n"/>
@@ -2853,7 +2891,7 @@
       <c r="G37" s="137" t="n"/>
       <c r="H37" s="154" t="n"/>
       <c r="I37" s="142">
-        <f>IF(G36="",I35+C36,I35+C36+G36)</f>
+        <f>IF(G37="",I36+C37,I36+C37+G37)</f>
         <v/>
       </c>
       <c r="J37" s="140" t="n"/>
@@ -2882,7 +2920,7 @@
       <c r="G38" s="137" t="n"/>
       <c r="H38" s="154" t="n"/>
       <c r="I38" s="144">
-        <f>IF(G37="",I36+C37,I36+C37+G37)</f>
+        <f>IF(G38="",I37+C38,I37+C38+G38)</f>
         <v/>
       </c>
       <c r="J38" s="140" t="n"/>
@@ -2911,7 +2949,7 @@
       <c r="G39" s="137" t="n"/>
       <c r="H39" s="154" t="n"/>
       <c r="I39" s="146">
-        <f>IF(G38="",I37+C38,I37+C38+G38)</f>
+        <f>IF(G39="",I38+C39,I38+C39+G39)</f>
         <v/>
       </c>
       <c r="J39" s="140" t="n"/>
@@ -2940,7 +2978,7 @@
       <c r="G40" s="137" t="n"/>
       <c r="H40" s="154" t="n"/>
       <c r="I40" s="139">
-        <f>IF(G39="",I38+C39,I38+C39+G39)</f>
+        <f>IF(G40="",I39+C40,I39+C40+G40)</f>
         <v/>
       </c>
       <c r="J40" s="140" t="n"/>
@@ -2969,7 +3007,7 @@
       <c r="G41" s="137" t="n"/>
       <c r="H41" s="154" t="n"/>
       <c r="I41" s="142">
-        <f>IF(G40="",I39+C40,I39+C40+G40)</f>
+        <f>IF(G41="",I40+C41,I40+C41+G41)</f>
         <v/>
       </c>
       <c r="J41" s="140" t="n"/>
@@ -2998,7 +3036,7 @@
       <c r="G42" s="137" t="n"/>
       <c r="H42" s="154" t="n"/>
       <c r="I42" s="144">
-        <f>IF(G41="",I40+C41,I40+C41+G41)</f>
+        <f>IF(G42="",I41+C42,I41+C42+G42)</f>
         <v/>
       </c>
       <c r="J42" s="140" t="n"/>
@@ -3027,7 +3065,7 @@
       <c r="G43" s="137" t="n"/>
       <c r="H43" s="154" t="n"/>
       <c r="I43" s="146">
-        <f>IF(G42="",I41+C42,I41+C42+G42)</f>
+        <f>IF(G43="",I42+C43,I42+C43+G43)</f>
         <v/>
       </c>
       <c r="J43" s="140" t="n"/>
@@ -3056,7 +3094,7 @@
       <c r="G44" s="137" t="n"/>
       <c r="H44" s="154" t="n"/>
       <c r="I44" s="139">
-        <f>IF(G43="",I42+C43,I42+C43+G43)</f>
+        <f>IF(G44="",I43+C44,I43+C44+G44)</f>
         <v/>
       </c>
       <c r="J44" s="140" t="n"/>
@@ -3085,7 +3123,7 @@
       <c r="G45" s="137" t="n"/>
       <c r="H45" s="154" t="n"/>
       <c r="I45" s="142">
-        <f>IF(G44="",I43+C44,I43+C44+G44)</f>
+        <f>IF(G45="",I44+C45,I44+C45+G45)</f>
         <v/>
       </c>
       <c r="J45" s="140" t="n"/>
@@ -3114,7 +3152,7 @@
       <c r="G46" s="137" t="n"/>
       <c r="H46" s="154" t="n"/>
       <c r="I46" s="144">
-        <f>IF(G45="",I44+C45,I44+C45+G45)</f>
+        <f>IF(G46="",I45+C46,I45+C46+G46)</f>
         <v/>
       </c>
       <c r="J46" s="140" t="n"/>
@@ -3143,7 +3181,7 @@
       <c r="G47" s="137" t="n"/>
       <c r="H47" s="154" t="n"/>
       <c r="I47" s="146">
-        <f>IF(G46="",I45+C46,I45+C46+G46)</f>
+        <f>IF(G47="",I46+C47,I46+C47+G47)</f>
         <v/>
       </c>
       <c r="J47" s="140" t="n"/>
@@ -3172,7 +3210,7 @@
       <c r="G48" s="137" t="n"/>
       <c r="H48" s="154" t="n"/>
       <c r="I48" s="139">
-        <f>IF(G47="",I46+C47,I46+C47+G47)</f>
+        <f>IF(G48="",I47+C48,I47+C48+G48)</f>
         <v/>
       </c>
       <c r="J48" s="140" t="n"/>
@@ -3201,7 +3239,7 @@
       <c r="G49" s="137" t="n"/>
       <c r="H49" s="154" t="n"/>
       <c r="I49" s="142">
-        <f>IF(G48="",I47+C48,I47+C48+G48)</f>
+        <f>IF(G49="",I48+C49,I48+C49+G49)</f>
         <v/>
       </c>
       <c r="J49" s="140" t="n"/>
@@ -3230,7 +3268,7 @@
       <c r="G50" s="137" t="n"/>
       <c r="H50" s="154" t="n"/>
       <c r="I50" s="144">
-        <f>IF(G49="",I48+C49,I48+C49+G49)</f>
+        <f>IF(G50="",I49+C50,I49+C50+G50)</f>
         <v/>
       </c>
       <c r="J50" s="140" t="n"/>
@@ -3259,7 +3297,7 @@
       <c r="G51" s="137" t="n"/>
       <c r="H51" s="154" t="n"/>
       <c r="I51" s="146">
-        <f>IF(G50="",I49+C50,I49+C50+G50)</f>
+        <f>IF(G51="",I50+C51,I50+C51+G51)</f>
         <v/>
       </c>
       <c r="J51" s="140" t="n"/>

--- a/PIC_2026_Tracker.xlsx
+++ b/PIC_2026_Tracker.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="148">
   <si>
     <t xml:space="preserve">PUNDICCI INVESTMENT COLLECTIVE — MASTER SUMMARY</t>
   </si>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Net P&amp;L</t>
   </si>
   <si>
-    <t xml:space="preserve">Account balance as at 07 Aug 2026: $7,097.51  ·  Net P&amp;L = Bet Return minus Stake (stake from captain's own pocket)</t>
+    <t xml:space="preserve">Account balance as at 09 Sep 2026: $7,175.51  ·  Net P&amp;L = Bet Return minus Stake (stake from captain's own pocket)  ·  Excludes Shannon's $10 AFL Premiership Exacta, live until 26 Sep</t>
   </si>
   <si>
     <t xml:space="preserve">PUNDICCI INVESTMENT COLLECTIVE — 2026 TRACKER</t>
@@ -345,19 +345,46 @@
     <t xml:space="preserve">08 Aug 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">15 Aug 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caulfield Heath R3 — Cavalry Girl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 Aug 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horses — bet lost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$20 of $30; balance on row 38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFL Premiership Exacta — Brisbane 1st / Sydney 2nd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.00</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pending</t>
   </si>
   <si>
-    <t xml:space="preserve">15 Aug 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 Aug 2026</t>
+    <t xml:space="preserve">LIVE — settles Grand Final 26 Sep. Potential return $180.00</t>
   </si>
   <si>
     <t xml:space="preserve">29 Aug 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Multi — Sydney Roosters + NZ All Blacks</t>
+  </si>
+  <si>
     <t xml:space="preserve">05 Sep 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-leg multi (horses &amp; sports)</t>
   </si>
   <si>
     <t xml:space="preserve">12 Sep 2026</t>
@@ -1405,8 +1432,8 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="4" t="n">
-        <f aca="false">'2026 Tracker'!I54</f>
-        <v>7098.91</v>
+        <f aca="false">'2026 Tracker'!I55</f>
+        <v>7176.91</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -1585,22 +1612,22 @@
         <v>9</v>
       </c>
       <c r="B14" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" s="10" t="n">
         <v>4</v>
       </c>
       <c r="E14" s="28" t="n">
-        <v>0.5</v>
+        <v>0.5556</v>
       </c>
       <c r="F14" s="29" t="n">
-        <v>480.95</v>
+        <v>558.95</v>
       </c>
       <c r="G14" s="30" t="n">
-        <v>270.95</v>
+        <v>318.95</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1608,22 +1635,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" s="31" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="32" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F15" s="33" t="n">
         <v>71.25</v>
       </c>
       <c r="G15" s="30" t="n">
-        <v>-48.75</v>
+        <v>-78.75</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1631,22 +1658,22 @@
         <v>18</v>
       </c>
       <c r="B16" s="34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" s="35" t="n">
-        <v>0.125</v>
+        <v>0.1111</v>
       </c>
       <c r="F16" s="36" t="n">
         <v>120</v>
       </c>
       <c r="G16" s="37" t="n">
-        <v>-120</v>
+        <v>-140</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1654,22 +1681,22 @@
         <v>13</v>
       </c>
       <c r="B17" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17" s="38" t="n">
-        <v>0.2222</v>
+        <v>0.1818</v>
       </c>
       <c r="F17" s="39" t="n">
         <v>287.74</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>37.74</v>
+        <v>-22.26</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1677,22 +1704,22 @@
         <v>22</v>
       </c>
       <c r="B18" s="25" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E18" s="41" t="n">
-        <v>0.2759</v>
+        <v>0.2647</v>
       </c>
       <c r="F18" s="26" t="n">
-        <v>959.94</v>
+        <v>1037.94</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>139.94</v>
+        <v>77.94</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1730,7 +1757,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -2779,24 +2806,28 @@
       <c r="C35" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="D35" s="46"/>
+      <c r="D35" s="46" t="s">
+        <v>42</v>
+      </c>
       <c r="E35" s="47"/>
       <c r="F35" s="52" t="n">
         <v>30</v>
       </c>
-      <c r="G35" s="48"/>
-      <c r="H35" s="65"/>
+      <c r="G35" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="65" t="s">
+        <v>43</v>
+      </c>
       <c r="I35" s="53" t="n">
         <f aca="false">IF(G35="",I34+C35,I34+C35+G35)</f>
         <v>7098.91</v>
       </c>
-      <c r="J35" s="51" t="s">
-        <v>107</v>
-      </c>
+      <c r="J35" s="51"/>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>9</v>
@@ -2804,24 +2835,30 @@
       <c r="C36" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="D36" s="46"/>
-      <c r="E36" s="47" t="n">
-        <v>30</v>
+      <c r="D36" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="E36" s="47" t="s">
+        <v>109</v>
       </c>
       <c r="F36" s="52" t="n">
         <v>30</v>
       </c>
-      <c r="G36" s="48"/>
-      <c r="H36" s="65"/>
+      <c r="G36" s="48" t="n">
+        <v>78</v>
+      </c>
+      <c r="H36" s="65" t="s">
+        <v>49</v>
+      </c>
       <c r="I36" s="53" t="n">
         <f aca="false">IF(G36="",I35+C36,I35+C36+G36)</f>
-        <v>7098.91</v>
+        <v>7176.91</v>
       </c>
       <c r="J36" s="51"/>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B37" s="20" t="s">
         <v>18</v>
@@ -2829,445 +2866,460 @@
       <c r="C37" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="D37" s="46"/>
-      <c r="E37" s="47" t="n">
-        <v>30</v>
-      </c>
+      <c r="D37" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="E37" s="47"/>
       <c r="F37" s="54" t="n">
-        <v>30</v>
-      </c>
-      <c r="G37" s="48"/>
-      <c r="H37" s="65"/>
+        <v>20</v>
+      </c>
+      <c r="G37" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="65" t="s">
+        <v>43</v>
+      </c>
       <c r="I37" s="55" t="n">
         <f aca="false">IF(G37="",I36+C37,I36+C37+G37)</f>
-        <v>7098.91</v>
-      </c>
-      <c r="J37" s="51"/>
+        <v>7176.91</v>
+      </c>
+      <c r="J37" s="51" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="E38" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="F38" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="G38" s="48"/>
+      <c r="H38" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="I38" s="55" t="n">
+        <f aca="false">IF(G38="",I37+C38,I37+C38+G38)</f>
+        <v>7176.91</v>
+      </c>
+      <c r="J38" s="51" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="B39" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C38" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="46"/>
-      <c r="E38" s="47" t="n">
-        <v>30</v>
-      </c>
-      <c r="F38" s="56" t="n">
-        <v>30</v>
-      </c>
-      <c r="G38" s="48"/>
-      <c r="H38" s="65"/>
-      <c r="I38" s="57" t="n">
-        <f aca="false">IF(G38="",I37+C38,I37+C38+G38)</f>
-        <v>7098.91</v>
-      </c>
-      <c r="J38" s="51"/>
-    </row>
-    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="B39" s="12" t="s">
+      <c r="C39" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="E39" s="47"/>
+      <c r="F39" s="56" t="n">
+        <v>30</v>
+      </c>
+      <c r="G39" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="65" t="s">
+        <v>43</v>
+      </c>
+      <c r="I39" s="57" t="n">
+        <f aca="false">IF(G39="",I38+C39,I38+C39+G39)</f>
+        <v>7176.91</v>
+      </c>
+      <c r="J39" s="51"/>
+    </row>
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="B40" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="46"/>
-      <c r="E39" s="47" t="n">
-        <v>30</v>
-      </c>
-      <c r="F39" s="45" t="n">
-        <v>30</v>
-      </c>
-      <c r="G39" s="48"/>
-      <c r="H39" s="65"/>
-      <c r="I39" s="50" t="n">
-        <f aca="false">IF(G39="",I38+C39,I38+C39+G39)</f>
-        <v>7098.91</v>
-      </c>
-      <c r="J39" s="51"/>
-    </row>
-    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="B40" s="6" t="s">
+      <c r="C40" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="E40" s="47"/>
+      <c r="F40" s="45" t="n">
+        <v>30</v>
+      </c>
+      <c r="G40" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="65" t="s">
+        <v>43</v>
+      </c>
+      <c r="I40" s="50" t="n">
+        <f aca="false">IF(G40="",I39+C40,I39+C40+G40)</f>
+        <v>7176.91</v>
+      </c>
+      <c r="J40" s="51"/>
+    </row>
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C40" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="46"/>
-      <c r="E40" s="47" t="n">
-        <v>30</v>
-      </c>
-      <c r="F40" s="52" t="n">
-        <v>30</v>
-      </c>
-      <c r="G40" s="48"/>
-      <c r="H40" s="65"/>
-      <c r="I40" s="53" t="n">
-        <f aca="false">IF(G40="",I39+C40,I39+C40+G40)</f>
-        <v>7098.91</v>
-      </c>
-      <c r="J40" s="51"/>
-    </row>
-    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="B41" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C41" s="54" t="n">
+      <c r="C41" s="52" t="n">
         <v>0</v>
       </c>
       <c r="D41" s="46"/>
-      <c r="E41" s="47" t="n">
-        <v>30</v>
-      </c>
-      <c r="F41" s="54" t="n">
+      <c r="E41" s="47"/>
+      <c r="F41" s="52" t="n">
         <v>30</v>
       </c>
       <c r="G41" s="48"/>
       <c r="H41" s="65"/>
-      <c r="I41" s="55" t="n">
+      <c r="I41" s="53" t="n">
         <f aca="false">IF(G41="",I40+C41,I40+C41+G41)</f>
-        <v>7098.91</v>
+        <v>7176.91</v>
       </c>
       <c r="J41" s="51"/>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C42" s="56" t="n">
+      <c r="A42" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="54" t="n">
         <v>0</v>
       </c>
       <c r="D42" s="46"/>
-      <c r="E42" s="47" t="n">
-        <v>30</v>
-      </c>
-      <c r="F42" s="56" t="n">
+      <c r="E42" s="47"/>
+      <c r="F42" s="54" t="n">
         <v>30</v>
       </c>
       <c r="G42" s="48"/>
       <c r="H42" s="65"/>
-      <c r="I42" s="57" t="n">
+      <c r="I42" s="55" t="n">
         <f aca="false">IF(G42="",I41+C42,I41+C42+G42)</f>
-        <v>7098.91</v>
+        <v>7176.91</v>
       </c>
       <c r="J42" s="51"/>
     </row>
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" s="45" t="n">
+      <c r="A43" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="56" t="n">
         <v>0</v>
       </c>
       <c r="D43" s="46"/>
-      <c r="E43" s="47" t="n">
-        <v>30</v>
-      </c>
-      <c r="F43" s="45" t="n">
+      <c r="E43" s="47"/>
+      <c r="F43" s="56" t="n">
         <v>30</v>
       </c>
       <c r="G43" s="48"/>
       <c r="H43" s="65"/>
-      <c r="I43" s="50" t="n">
+      <c r="I43" s="57" t="n">
         <f aca="false">IF(G43="",I42+C43,I42+C43+G43)</f>
-        <v>7098.91</v>
+        <v>7176.91</v>
       </c>
       <c r="J43" s="51"/>
     </row>
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" s="52" t="n">
+      <c r="A44" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="45" t="n">
         <v>0</v>
       </c>
       <c r="D44" s="46"/>
-      <c r="E44" s="47" t="n">
-        <v>30</v>
-      </c>
-      <c r="F44" s="52" t="n">
+      <c r="E44" s="47"/>
+      <c r="F44" s="45" t="n">
         <v>30</v>
       </c>
       <c r="G44" s="48"/>
       <c r="H44" s="65"/>
-      <c r="I44" s="53" t="n">
+      <c r="I44" s="50" t="n">
         <f aca="false">IF(G44="",I43+C44,I43+C44+G44)</f>
-        <v>7098.91</v>
+        <v>7176.91</v>
       </c>
       <c r="J44" s="51"/>
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="34" t="s">
-        <v>117</v>
-      </c>
-      <c r="B45" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C45" s="54" t="n">
+      <c r="A45" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" s="52" t="n">
         <v>0</v>
       </c>
       <c r="D45" s="46"/>
-      <c r="E45" s="47" t="n">
-        <v>30</v>
-      </c>
-      <c r="F45" s="54" t="n">
+      <c r="E45" s="47"/>
+      <c r="F45" s="52" t="n">
         <v>30</v>
       </c>
       <c r="G45" s="48"/>
       <c r="H45" s="65"/>
-      <c r="I45" s="55" t="n">
+      <c r="I45" s="53" t="n">
         <f aca="false">IF(G45="",I44+C45,I44+C45+G45)</f>
-        <v>7098.91</v>
+        <v>7176.91</v>
       </c>
       <c r="J45" s="51"/>
     </row>
     <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C46" s="56" t="n">
+      <c r="A46" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="54" t="n">
         <v>0</v>
       </c>
       <c r="D46" s="46"/>
-      <c r="E46" s="47" t="n">
-        <v>30</v>
-      </c>
-      <c r="F46" s="56" t="n">
+      <c r="E46" s="47"/>
+      <c r="F46" s="54" t="n">
         <v>30</v>
       </c>
       <c r="G46" s="48"/>
       <c r="H46" s="65"/>
-      <c r="I46" s="57" t="n">
+      <c r="I46" s="55" t="n">
         <f aca="false">IF(G46="",I45+C46,I45+C46+G46)</f>
-        <v>7098.91</v>
+        <v>7176.91</v>
       </c>
       <c r="J46" s="51"/>
     </row>
     <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C47" s="45" t="n">
+      <c r="A47" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" s="56" t="n">
         <v>0</v>
       </c>
       <c r="D47" s="46"/>
-      <c r="E47" s="47" t="n">
-        <v>30</v>
-      </c>
-      <c r="F47" s="45" t="n">
+      <c r="E47" s="47"/>
+      <c r="F47" s="56" t="n">
         <v>30</v>
       </c>
       <c r="G47" s="48"/>
       <c r="H47" s="65"/>
-      <c r="I47" s="50" t="n">
+      <c r="I47" s="57" t="n">
         <f aca="false">IF(G47="",I46+C47,I46+C47+G47)</f>
-        <v>7098.91</v>
+        <v>7176.91</v>
       </c>
       <c r="J47" s="51"/>
     </row>
     <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C48" s="52" t="n">
+      <c r="A48" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" s="45" t="n">
         <v>0</v>
       </c>
       <c r="D48" s="46"/>
-      <c r="E48" s="47" t="n">
-        <v>30</v>
-      </c>
-      <c r="F48" s="52" t="n">
+      <c r="E48" s="47"/>
+      <c r="F48" s="45" t="n">
         <v>30</v>
       </c>
       <c r="G48" s="48"/>
       <c r="H48" s="65"/>
-      <c r="I48" s="53" t="n">
+      <c r="I48" s="50" t="n">
         <f aca="false">IF(G48="",I47+C48,I47+C48+G48)</f>
-        <v>7098.91</v>
+        <v>7176.91</v>
       </c>
       <c r="J48" s="51"/>
     </row>
     <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="B49" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C49" s="54" t="n">
+      <c r="A49" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" s="52" t="n">
         <v>0</v>
       </c>
       <c r="D49" s="46"/>
-      <c r="E49" s="47" t="n">
-        <v>30</v>
-      </c>
-      <c r="F49" s="54" t="n">
+      <c r="E49" s="47"/>
+      <c r="F49" s="52" t="n">
         <v>30</v>
       </c>
       <c r="G49" s="48"/>
       <c r="H49" s="65"/>
-      <c r="I49" s="55" t="n">
+      <c r="I49" s="53" t="n">
         <f aca="false">IF(G49="",I48+C49,I48+C49+G49)</f>
-        <v>7098.91</v>
+        <v>7176.91</v>
       </c>
       <c r="J49" s="51"/>
     </row>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B50" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C50" s="56" t="n">
+      <c r="A50" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="54" t="n">
         <v>0</v>
       </c>
       <c r="D50" s="46"/>
-      <c r="E50" s="47" t="n">
-        <v>30</v>
-      </c>
-      <c r="F50" s="56" t="n">
+      <c r="E50" s="47"/>
+      <c r="F50" s="54" t="n">
         <v>30</v>
       </c>
       <c r="G50" s="48"/>
       <c r="H50" s="65"/>
-      <c r="I50" s="57" t="n">
+      <c r="I50" s="55" t="n">
         <f aca="false">IF(G50="",I49+C50,I49+C50+G50)</f>
-        <v>7098.91</v>
+        <v>7176.91</v>
       </c>
       <c r="J50" s="51"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="45" t="n">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51" s="56" t="n">
         <v>0</v>
       </c>
       <c r="D51" s="46"/>
-      <c r="E51" s="47" t="n">
-        <v>30</v>
-      </c>
-      <c r="F51" s="45" t="n">
+      <c r="E51" s="47"/>
+      <c r="F51" s="56" t="n">
         <v>30</v>
       </c>
       <c r="G51" s="48"/>
       <c r="H51" s="65"/>
-      <c r="I51" s="50" t="n">
+      <c r="I51" s="57" t="n">
         <f aca="false">IF(G51="",I50+C51,I50+C51+G51)</f>
-        <v>7098.91</v>
+        <v>7176.91</v>
       </c>
       <c r="J51" s="51"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C52" s="52" t="n">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="45" t="n">
         <v>0</v>
       </c>
       <c r="D52" s="46"/>
-      <c r="E52" s="47" t="n">
-        <v>30</v>
-      </c>
-      <c r="F52" s="52" t="n">
+      <c r="E52" s="47"/>
+      <c r="F52" s="45" t="n">
         <v>30</v>
       </c>
       <c r="G52" s="48"/>
       <c r="H52" s="65"/>
-      <c r="I52" s="53" t="n">
+      <c r="I52" s="50" t="n">
         <f aca="false">IF(G52="",I51+C52,I51+C52+G52)</f>
-        <v>7098.91</v>
+        <v>7176.91</v>
       </c>
       <c r="J52" s="51"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="34" t="s">
-        <v>125</v>
-      </c>
-      <c r="B53" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C53" s="54" t="n">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" s="52" t="n">
         <v>0</v>
       </c>
       <c r="D53" s="46"/>
-      <c r="E53" s="47" t="n">
-        <v>30</v>
-      </c>
-      <c r="F53" s="54" t="n">
+      <c r="E53" s="47"/>
+      <c r="F53" s="52" t="n">
         <v>30</v>
       </c>
       <c r="G53" s="48"/>
       <c r="H53" s="65"/>
-      <c r="I53" s="55" t="n">
+      <c r="I53" s="53" t="n">
         <f aca="false">IF(G53="",I52+C53,I52+C53+G53)</f>
-        <v>7098.91</v>
+        <v>7176.91</v>
       </c>
       <c r="J53" s="51"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="B54" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C54" s="56" t="n">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="B54" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="54" t="n">
         <v>0</v>
       </c>
       <c r="D54" s="46"/>
-      <c r="E54" s="47" t="n">
-        <v>30</v>
-      </c>
-      <c r="F54" s="56" t="n">
+      <c r="E54" s="47"/>
+      <c r="F54" s="54" t="n">
         <v>30</v>
       </c>
       <c r="G54" s="48"/>
       <c r="H54" s="65"/>
-      <c r="I54" s="57" t="n">
+      <c r="I54" s="55" t="n">
         <f aca="false">IF(G54="",I53+C54,I53+C54+G54)</f>
-        <v>7098.91</v>
+        <v>7176.91</v>
       </c>
       <c r="J54" s="51"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C55" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="46"/>
+      <c r="E55" s="47"/>
+      <c r="F55" s="56" t="n">
+        <v>30</v>
+      </c>
+      <c r="G55" s="48"/>
+      <c r="H55" s="65"/>
+      <c r="I55" s="57" t="n">
+        <f aca="false">IF(G55="",I54+C55,I54+C55+G55)</f>
+        <v>7176.91</v>
+      </c>
+      <c r="J55" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3300,7 +3352,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="43" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B1" s="43"/>
       <c r="C1" s="43"/>
@@ -3313,16 +3365,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>27</v>
@@ -3338,7 +3390,7 @@
       </c>
       <c r="C3" s="66" t="n">
         <f aca="false">SUMIF('2026 Tracker'!B3:B50,A3,'2026 Tracker'!E3:E50)</f>
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="D3" s="39" t="n">
         <f aca="false">SUMIF('2026 Tracker'!B3:B50,A3,'2026 Tracker'!F3:F50)</f>
@@ -3346,7 +3398,7 @@
       </c>
       <c r="E3" s="67" t="n">
         <f aca="false">D3-C3</f>
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="F3" s="68" t="n">
         <f aca="false">IFERROR(COUNTIFS('2026 Tracker'!B3:B50,A3,'2026 Tracker'!G3:G50,"Win")/COUNTIFS('2026 Tracker'!B3:B50,A3,'2026 Tracker'!G3:G50,"&lt;&gt;"),"-")</f>
@@ -3363,7 +3415,7 @@
       </c>
       <c r="C4" s="69" t="n">
         <f aca="false">SUMIF('2026 Tracker'!B3:B50,A4,'2026 Tracker'!E3:E50)</f>
-        <v>200.13</v>
+        <v>80.13</v>
       </c>
       <c r="D4" s="29" t="n">
         <f aca="false">SUMIF('2026 Tracker'!B3:B50,A4,'2026 Tracker'!F3:F50)</f>
@@ -3371,7 +3423,7 @@
       </c>
       <c r="E4" s="70" t="n">
         <f aca="false">D4-C4</f>
-        <v>129.87</v>
+        <v>249.87</v>
       </c>
       <c r="F4" s="71" t="n">
         <f aca="false">IFERROR(COUNTIFS('2026 Tracker'!B3:B50,A4,'2026 Tracker'!G3:G50,"Win")/COUNTIFS('2026 Tracker'!B3:B50,A4,'2026 Tracker'!G3:G50,"&lt;&gt;"),"-")</f>
@@ -3384,11 +3436,11 @@
       </c>
       <c r="B5" s="34" t="n">
         <f aca="false">COUNTIF('2026 Tracker'!B3:B50,A5)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="72" t="n">
         <f aca="false">SUMIF('2026 Tracker'!B3:B50,A5,'2026 Tracker'!E3:E50)</f>
-        <v>187.9</v>
+        <v>67.9</v>
       </c>
       <c r="D5" s="36" t="n">
         <f aca="false">SUMIF('2026 Tracker'!B3:B50,A5,'2026 Tracker'!F3:F50)</f>
@@ -3396,7 +3448,7 @@
       </c>
       <c r="E5" s="73" t="n">
         <f aca="false">D5-C5</f>
-        <v>172.1</v>
+        <v>292.1</v>
       </c>
       <c r="F5" s="74" t="n">
         <f aca="false">IFERROR(COUNTIFS('2026 Tracker'!B3:B50,A5,'2026 Tracker'!G3:G50,"Win")/COUNTIFS('2026 Tracker'!B3:B50,A5,'2026 Tracker'!G3:G50,"&lt;&gt;"),"-")</f>
@@ -3409,19 +3461,19 @@
       </c>
       <c r="B6" s="31" t="n">
         <f aca="false">COUNTIF('2026 Tracker'!B3:B50,A6)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="75" t="n">
         <f aca="false">SUMIF('2026 Tracker'!B3:B50,A6,'2026 Tracker'!E3:E50)</f>
-        <v>212.37</v>
+        <v>92.37</v>
       </c>
       <c r="D6" s="33" t="n">
         <f aca="false">SUMIF('2026 Tracker'!B3:B50,A6,'2026 Tracker'!F3:F50)</f>
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="E6" s="76" t="n">
         <f aca="false">D6-C6</f>
-        <v>117.63</v>
+        <v>207.63</v>
       </c>
       <c r="F6" s="77" t="n">
         <f aca="false">IFERROR(COUNTIFS('2026 Tracker'!B3:B50,A6,'2026 Tracker'!G3:G50,"Win")/COUNTIFS('2026 Tracker'!B3:B50,A6,'2026 Tracker'!G3:G50,"&lt;&gt;"),"-")</f>
@@ -3430,7 +3482,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="78" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B7" s="78"/>
       <c r="C7" s="78"/>
@@ -3438,15 +3490,15 @@
       <c r="E7" s="78"/>
       <c r="F7" s="79" t="n">
         <f aca="false">'2026 Tracker'!I50</f>
-        <v>7098.91</v>
+        <v>7176.91</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="80" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B9" s="81" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C9" s="81"/>
       <c r="D9" s="81"/>
@@ -3455,7 +3507,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="82" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="82"/>
@@ -3467,7 +3519,7 @@
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="84" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B13" s="84"/>
       <c r="C13" s="84"/>
@@ -3480,7 +3532,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="86" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C14" s="86"/>
       <c r="D14" s="86"/>
@@ -3494,7 +3546,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C15" s="86"/>
       <c r="D15" s="86"/>
@@ -3508,7 +3560,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="86" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C16" s="86"/>
       <c r="D16" s="86"/>
